--- a/mca_sem/static/TR/MCA_1_TR_FORMATE.xlsx
+++ b/mca_sem/static/TR/MCA_1_TR_FORMATE.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="MCA1st" sheetId="4" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
   <si>
     <t xml:space="preserve"> Purnea University, Purnia, Bihar</t>
   </si>
@@ -62,12 +62,12 @@
     <t xml:space="preserve">1MCACCE(C) </t>
   </si>
   <si>
-    <t>1MCASEC(A)</t>
-  </si>
-  <si>
     <t>1MCASEC(C)</t>
   </si>
   <si>
+    <t>1MCASEC(D)</t>
+  </si>
+  <si>
     <t>1MCACCC4</t>
   </si>
   <si>
@@ -134,6 +134,9 @@
     <t>2418M240001</t>
   </si>
   <si>
+    <t>AB</t>
+  </si>
+  <si>
     <t>FAIL</t>
   </si>
   <si>
@@ -183,6 +186,9 @@
   </si>
   <si>
     <t>Full Signature of Tabulator-cum-scrutinizer with date</t>
+  </si>
+  <si>
+    <t>Controller of Examination</t>
   </si>
   <si>
     <t>Fail: 01</t>
@@ -1004,7 +1010,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1048,15 +1054,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1095,13 +1092,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1645,20 +1642,20 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="30" t="s">
+      <c r="R4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-      <c r="Y4" s="30"/>
-      <c r="Z4" s="30"/>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="30"/>
-      <c r="AC4" s="30"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="27"/>
     </row>
     <row r="5" ht="22.8" spans="1:29">
       <c r="A5" s="7"/>
@@ -1678,20 +1675,20 @@
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
-      <c r="R5" s="30" t="s">
+      <c r="R5" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="S5" s="30"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
-      <c r="Z5" s="30"/>
-      <c r="AA5" s="30"/>
-      <c r="AB5" s="30"/>
-      <c r="AC5" s="30"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="27"/>
+      <c r="AC5" s="27"/>
     </row>
     <row r="6" ht="26.25" customHeight="1" spans="1:29">
       <c r="A6" s="8" t="s">
@@ -1713,20 +1710,20 @@
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
-      <c r="R6" s="31" t="s">
+      <c r="R6" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="S6" s="31"/>
-      <c r="T6" s="31"/>
-      <c r="U6" s="31"/>
-      <c r="V6" s="31"/>
-      <c r="W6" s="31"/>
-      <c r="X6" s="31"/>
-      <c r="Y6" s="31"/>
-      <c r="Z6" s="31"/>
-      <c r="AA6" s="31"/>
-      <c r="AB6" s="31"/>
-      <c r="AC6" s="31"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="28"/>
+      <c r="W6" s="28"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="28"/>
+      <c r="AB6" s="28"/>
+      <c r="AC6" s="28"/>
     </row>
     <row r="7" ht="26.25" customHeight="1" spans="1:29">
       <c r="A7" s="9"/>
@@ -1771,13 +1768,13 @@
       <c r="Z7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AA7" s="32" t="s">
+      <c r="AA7" s="29" t="s">
         <v>14</v>
       </c>
       <c r="AB7" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="AC7" s="33" t="s">
+      <c r="AC7" s="30" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1830,9 +1827,9 @@
       <c r="Z8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AA8" s="34"/>
+      <c r="AA8" s="31"/>
       <c r="AB8" s="12"/>
-      <c r="AC8" s="33"/>
+      <c r="AC8" s="30"/>
     </row>
     <row r="9" ht="219" customHeight="1" spans="1:29">
       <c r="A9" s="12"/>
@@ -1903,9 +1900,9 @@
         <v>30</v>
       </c>
       <c r="Z9" s="12"/>
-      <c r="AA9" s="35"/>
+      <c r="AA9" s="32"/>
       <c r="AB9" s="12"/>
-      <c r="AC9" s="33"/>
+      <c r="AC9" s="30"/>
     </row>
     <row r="10" ht="33.75" customHeight="1" spans="1:29">
       <c r="A10" s="12"/>
@@ -1984,7 +1981,7 @@
         <v>800</v>
       </c>
       <c r="AB10" s="12"/>
-      <c r="AC10" s="33"/>
+      <c r="AC10" s="30"/>
     </row>
     <row r="11" ht="33" customHeight="1" spans="1:29">
       <c r="A11" s="12"/>
@@ -2050,7 +2047,7 @@
         <v>360</v>
       </c>
       <c r="AB11" s="12"/>
-      <c r="AC11" s="33"/>
+      <c r="AC11" s="30"/>
     </row>
     <row r="12" ht="33.75" customHeight="1" spans="1:29">
       <c r="A12" s="19">
@@ -2071,7 +2068,7 @@
       <c r="F12" s="19">
         <v>6</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="19">
         <v>7</v>
       </c>
       <c r="H12" s="19">
@@ -2080,7 +2077,7 @@
       <c r="I12" s="19">
         <v>9</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="19">
         <v>10</v>
       </c>
       <c r="K12" s="19">
@@ -2089,7 +2086,7 @@
       <c r="L12" s="19">
         <v>12</v>
       </c>
-      <c r="M12" s="20">
+      <c r="M12" s="19">
         <v>13</v>
       </c>
       <c r="N12" s="19">
@@ -2098,7 +2095,7 @@
       <c r="O12" s="19">
         <v>15</v>
       </c>
-      <c r="P12" s="20">
+      <c r="P12" s="19">
         <v>16</v>
       </c>
       <c r="Q12" s="19">
@@ -2107,7 +2104,7 @@
       <c r="R12" s="19">
         <v>18</v>
       </c>
-      <c r="S12" s="20">
+      <c r="S12" s="19">
         <v>19</v>
       </c>
       <c r="T12" s="19">
@@ -2116,7 +2113,7 @@
       <c r="U12" s="19">
         <v>21</v>
       </c>
-      <c r="V12" s="20">
+      <c r="V12" s="19">
         <v>22</v>
       </c>
       <c r="W12" s="19">
@@ -2125,10 +2122,10 @@
       <c r="X12" s="19">
         <v>24</v>
       </c>
-      <c r="Y12" s="20">
+      <c r="Y12" s="19">
         <v>25</v>
       </c>
-      <c r="Z12" s="20">
+      <c r="Z12" s="19">
         <v>26</v>
       </c>
       <c r="AA12" s="19">
@@ -2142,354 +2139,354 @@
       </c>
     </row>
     <row r="13" ht="33.75" customHeight="1" spans="1:29">
-      <c r="A13" s="21">
+      <c r="A13" s="20">
         <v>1800001</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21">
-        <v>0</v>
-      </c>
-      <c r="F13" s="21">
+      <c r="D13" s="20"/>
+      <c r="E13" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="20">
         <v>28</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="20">
         <v>28</v>
       </c>
-      <c r="H13" s="21">
-        <v>0</v>
-      </c>
-      <c r="I13" s="21">
+      <c r="H13" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="20">
         <v>26</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13" s="20">
         <v>26</v>
       </c>
-      <c r="K13" s="21">
-        <v>0</v>
-      </c>
-      <c r="L13" s="21">
+      <c r="K13" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="20">
         <v>25</v>
       </c>
-      <c r="M13" s="22">
+      <c r="M13" s="20">
         <v>25</v>
       </c>
-      <c r="N13" s="21">
-        <v>0</v>
-      </c>
-      <c r="O13" s="21">
+      <c r="N13" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="O13" s="20">
         <v>28</v>
       </c>
-      <c r="P13" s="22">
+      <c r="P13" s="20">
         <v>28</v>
       </c>
-      <c r="Q13" s="21">
-        <v>0</v>
-      </c>
-      <c r="R13" s="21">
+      <c r="Q13" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="R13" s="20">
         <v>28</v>
       </c>
-      <c r="S13" s="22">
+      <c r="S13" s="20">
         <v>28</v>
       </c>
-      <c r="T13" s="21">
-        <v>0</v>
-      </c>
-      <c r="U13" s="21">
+      <c r="T13" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="U13" s="20">
         <v>27</v>
       </c>
-      <c r="V13" s="22">
+      <c r="V13" s="20">
         <v>27</v>
       </c>
-      <c r="W13" s="21">
-        <v>0</v>
-      </c>
-      <c r="X13" s="21">
+      <c r="W13" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="X13" s="20">
         <v>26</v>
       </c>
-      <c r="Y13" s="22">
+      <c r="Y13" s="20">
         <v>26</v>
       </c>
-      <c r="Z13" s="22">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="21">
+      <c r="Z13" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA13" s="20">
         <v>188</v>
       </c>
-      <c r="AB13" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC13" s="21"/>
+      <c r="AB13" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC13" s="20"/>
     </row>
     <row r="14" ht="33.75" customHeight="1" spans="1:29">
-      <c r="A14" s="21">
+      <c r="A14" s="20">
         <v>1800002</v>
       </c>
-      <c r="B14" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="21" t="s">
+      <c r="B14" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21">
+      <c r="C14" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20">
         <v>57</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="20">
         <v>27</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="20">
         <v>84</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="20">
         <v>58</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="20">
         <v>27</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14" s="20">
         <v>85</v>
       </c>
-      <c r="K14" s="21">
+      <c r="K14" s="20">
         <v>54</v>
       </c>
-      <c r="L14" s="21">
+      <c r="L14" s="20">
         <v>27</v>
       </c>
-      <c r="M14" s="22">
+      <c r="M14" s="20">
         <v>81</v>
       </c>
-      <c r="N14" s="21">
+      <c r="N14" s="20">
         <v>59</v>
       </c>
-      <c r="O14" s="21">
+      <c r="O14" s="20">
         <v>27</v>
       </c>
-      <c r="P14" s="22">
+      <c r="P14" s="20">
         <v>86</v>
       </c>
-      <c r="Q14" s="21">
+      <c r="Q14" s="20">
         <v>55</v>
       </c>
-      <c r="R14" s="21">
+      <c r="R14" s="20">
         <v>27</v>
       </c>
-      <c r="S14" s="22">
+      <c r="S14" s="20">
         <v>82</v>
       </c>
-      <c r="T14" s="21">
+      <c r="T14" s="20">
         <v>57</v>
       </c>
-      <c r="U14" s="21">
+      <c r="U14" s="20">
         <v>27</v>
       </c>
-      <c r="V14" s="22">
+      <c r="V14" s="20">
         <v>84</v>
       </c>
-      <c r="W14" s="21">
+      <c r="W14" s="20">
         <v>59</v>
       </c>
-      <c r="X14" s="21">
+      <c r="X14" s="20">
         <v>27</v>
       </c>
-      <c r="Y14" s="22">
+      <c r="Y14" s="20">
         <v>86</v>
       </c>
-      <c r="Z14" s="22">
+      <c r="Z14" s="20">
         <v>95</v>
       </c>
-      <c r="AA14" s="21">
+      <c r="AA14" s="20">
         <v>683</v>
       </c>
-      <c r="AB14" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC14" s="21"/>
+      <c r="AB14" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC14" s="20"/>
     </row>
     <row r="15" ht="33.75" customHeight="1" spans="1:29">
-      <c r="A15" s="21">
+      <c r="A15" s="20">
         <v>1800003</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20">
+        <v>54</v>
+      </c>
+      <c r="F15" s="20">
+        <v>28</v>
+      </c>
+      <c r="G15" s="20">
+        <v>82</v>
+      </c>
+      <c r="H15" s="20">
+        <v>53</v>
+      </c>
+      <c r="I15" s="20">
+        <v>27</v>
+      </c>
+      <c r="J15" s="20">
+        <v>80</v>
+      </c>
+      <c r="K15" s="20">
+        <v>55</v>
+      </c>
+      <c r="L15" s="20">
+        <v>27</v>
+      </c>
+      <c r="M15" s="20">
+        <v>82</v>
+      </c>
+      <c r="N15" s="20">
+        <v>57</v>
+      </c>
+      <c r="O15" s="20">
+        <v>25</v>
+      </c>
+      <c r="P15" s="20">
+        <v>82</v>
+      </c>
+      <c r="Q15" s="20">
+        <v>55</v>
+      </c>
+      <c r="R15" s="20">
+        <v>26</v>
+      </c>
+      <c r="S15" s="20">
+        <v>81</v>
+      </c>
+      <c r="T15" s="20">
+        <v>58</v>
+      </c>
+      <c r="U15" s="20">
+        <v>28</v>
+      </c>
+      <c r="V15" s="20">
+        <v>86</v>
+      </c>
+      <c r="W15" s="20">
+        <v>57</v>
+      </c>
+      <c r="X15" s="20">
+        <v>27</v>
+      </c>
+      <c r="Y15" s="20">
+        <v>84</v>
+      </c>
+      <c r="Z15" s="20">
+        <v>93</v>
+      </c>
+      <c r="AA15" s="20">
+        <v>670</v>
+      </c>
+      <c r="AB15" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21">
-        <v>54</v>
-      </c>
-      <c r="F15" s="21">
-        <v>28</v>
-      </c>
-      <c r="G15" s="22">
-        <v>82</v>
-      </c>
-      <c r="H15" s="21">
-        <v>53</v>
-      </c>
-      <c r="I15" s="21">
-        <v>27</v>
-      </c>
-      <c r="J15" s="22">
-        <v>80</v>
-      </c>
-      <c r="K15" s="21">
-        <v>55</v>
-      </c>
-      <c r="L15" s="21">
-        <v>27</v>
-      </c>
-      <c r="M15" s="22">
-        <v>82</v>
-      </c>
-      <c r="N15" s="21">
-        <v>57</v>
-      </c>
-      <c r="O15" s="21">
-        <v>25</v>
-      </c>
-      <c r="P15" s="22">
-        <v>82</v>
-      </c>
-      <c r="Q15" s="21">
-        <v>55</v>
-      </c>
-      <c r="R15" s="21">
-        <v>26</v>
-      </c>
-      <c r="S15" s="22">
-        <v>81</v>
-      </c>
-      <c r="T15" s="21">
-        <v>58</v>
-      </c>
-      <c r="U15" s="21">
-        <v>28</v>
-      </c>
-      <c r="V15" s="22">
-        <v>86</v>
-      </c>
-      <c r="W15" s="21">
-        <v>57</v>
-      </c>
-      <c r="X15" s="21">
-        <v>27</v>
-      </c>
-      <c r="Y15" s="22">
-        <v>84</v>
-      </c>
-      <c r="Z15" s="22">
-        <v>93</v>
-      </c>
-      <c r="AA15" s="21">
-        <v>670</v>
-      </c>
-      <c r="AB15" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC15" s="21"/>
+      <c r="AC15" s="20"/>
     </row>
     <row r="16" ht="33.75" customHeight="1" spans="1:29">
-      <c r="A16" s="21">
+      <c r="A16" s="20">
         <v>1800004</v>
       </c>
-      <c r="B16" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="21" t="s">
+      <c r="B16" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21">
+      <c r="C16" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20">
         <v>50</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="20">
         <v>28</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="20">
         <v>78</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="20">
         <v>46</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="20">
         <v>26</v>
       </c>
-      <c r="J16" s="22">
+      <c r="J16" s="20">
         <v>72</v>
       </c>
-      <c r="K16" s="21">
+      <c r="K16" s="20">
         <v>52</v>
       </c>
-      <c r="L16" s="21">
+      <c r="L16" s="20">
         <v>26</v>
       </c>
-      <c r="M16" s="22">
+      <c r="M16" s="20">
         <v>78</v>
       </c>
-      <c r="N16" s="21">
+      <c r="N16" s="20">
         <v>49</v>
       </c>
-      <c r="O16" s="21">
+      <c r="O16" s="20">
         <v>26</v>
       </c>
-      <c r="P16" s="22">
+      <c r="P16" s="20">
         <v>75</v>
       </c>
-      <c r="Q16" s="21">
+      <c r="Q16" s="20">
         <v>47</v>
       </c>
-      <c r="R16" s="21">
+      <c r="R16" s="20">
         <v>28</v>
       </c>
-      <c r="S16" s="22">
+      <c r="S16" s="20">
         <v>75</v>
       </c>
-      <c r="T16" s="21">
+      <c r="T16" s="20">
         <v>57</v>
       </c>
-      <c r="U16" s="21">
+      <c r="U16" s="20">
         <v>27</v>
       </c>
-      <c r="V16" s="22">
+      <c r="V16" s="20">
         <v>84</v>
       </c>
-      <c r="W16" s="21">
+      <c r="W16" s="20">
         <v>56</v>
       </c>
-      <c r="X16" s="21">
+      <c r="X16" s="20">
         <v>26</v>
       </c>
-      <c r="Y16" s="22">
+      <c r="Y16" s="20">
         <v>82</v>
       </c>
-      <c r="Z16" s="22">
+      <c r="Z16" s="20">
         <v>92</v>
       </c>
-      <c r="AA16" s="21">
+      <c r="AA16" s="20">
         <v>636</v>
       </c>
-      <c r="AB16" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC16" s="21"/>
+      <c r="AB16" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC16" s="20"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="35" customHeight="1" spans="1:29">
       <c r="A17" s="16">
         <v>1800005</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" s="16"/>
       <c r="E17" s="16">
@@ -2498,7 +2495,7 @@
       <c r="F17" s="16">
         <v>27</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="16">
         <v>87</v>
       </c>
       <c r="H17" s="16">
@@ -2507,7 +2504,7 @@
       <c r="I17" s="16">
         <v>27</v>
       </c>
-      <c r="J17" s="23">
+      <c r="J17" s="16">
         <v>83</v>
       </c>
       <c r="K17" s="16">
@@ -2516,7 +2513,7 @@
       <c r="L17" s="16">
         <v>27</v>
       </c>
-      <c r="M17" s="23">
+      <c r="M17" s="16">
         <v>84</v>
       </c>
       <c r="N17" s="16">
@@ -2525,7 +2522,7 @@
       <c r="O17" s="16">
         <v>27</v>
       </c>
-      <c r="P17" s="23">
+      <c r="P17" s="16">
         <v>88</v>
       </c>
       <c r="Q17" s="16">
@@ -2534,7 +2531,7 @@
       <c r="R17" s="16">
         <v>28</v>
       </c>
-      <c r="S17" s="23">
+      <c r="S17" s="16">
         <v>88</v>
       </c>
       <c r="T17" s="16">
@@ -2543,7 +2540,7 @@
       <c r="U17" s="16">
         <v>27</v>
       </c>
-      <c r="V17" s="23">
+      <c r="V17" s="16">
         <v>81</v>
       </c>
       <c r="W17" s="16">
@@ -2552,292 +2549,291 @@
       <c r="X17" s="16">
         <v>27</v>
       </c>
-      <c r="Y17" s="23">
+      <c r="Y17" s="16">
         <v>82</v>
       </c>
-      <c r="Z17" s="23">
+      <c r="Z17" s="16">
         <v>92</v>
       </c>
-      <c r="AA17" s="23">
+      <c r="AA17" s="16">
         <v>685</v>
       </c>
-      <c r="AB17" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC17" s="36"/>
+      <c r="AB17" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC17" s="33"/>
     </row>
     <row r="18" spans="27:28">
-      <c r="AA18" s="37"/>
-      <c r="AB18" s="38"/>
+      <c r="AA18" s="34"/>
+      <c r="AB18" s="35"/>
     </row>
     <row r="19" ht="15" customHeight="1" spans="27:28">
-      <c r="AA19" s="37"/>
-      <c r="AB19" s="38"/>
+      <c r="AA19" s="34"/>
+      <c r="AB19" s="35"/>
     </row>
     <row r="20" spans="27:28">
-      <c r="AA20" s="37"/>
-      <c r="AB20" s="38"/>
+      <c r="AA20" s="34"/>
+      <c r="AB20" s="35"/>
     </row>
     <row r="21" spans="27:28">
-      <c r="AA21" s="37"/>
-      <c r="AB21" s="38"/>
+      <c r="AA21" s="34"/>
+      <c r="AB21" s="35"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="13.2" spans="1:29">
-      <c r="A22" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="25"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="25"/>
-      <c r="S22" s="25"/>
-      <c r="T22" s="25"/>
-      <c r="U22" s="25"/>
-      <c r="V22" s="25"/>
-      <c r="W22" s="25"/>
-      <c r="X22" s="25"/>
-      <c r="Y22" s="25"/>
-      <c r="Z22" s="25"/>
-      <c r="AA22" s="39"/>
-      <c r="AB22" s="25"/>
-      <c r="AC22" s="26"/>
+      <c r="A22" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="22"/>
+      <c r="S22" s="22"/>
+      <c r="T22" s="22"/>
+      <c r="U22" s="22"/>
+      <c r="V22" s="22"/>
+      <c r="W22" s="22"/>
+      <c r="X22" s="22"/>
+      <c r="Y22" s="22"/>
+      <c r="Z22" s="22"/>
+      <c r="AA22" s="36"/>
+      <c r="AB22" s="22"/>
+      <c r="AC22" s="23"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="13.2" spans="1:33">
-      <c r="A23" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26" t="s">
+      <c r="A23" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="25" t="s">
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="J23" s="25"/>
-      <c r="K23" s="27" t="s">
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="25" t="s">
+      <c r="J23" s="22"/>
+      <c r="K23" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="25"/>
-      <c r="S23" s="25"/>
-      <c r="T23" s="25"/>
-      <c r="U23" s="25"/>
-      <c r="V23" s="25"/>
-      <c r="W23" s="25"/>
-      <c r="X23" s="25"/>
-      <c r="Y23" s="25"/>
-      <c r="Z23" s="25"/>
-      <c r="AA23" s="25" t="s">
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AB23" s="25"/>
-      <c r="AC23" s="40"/>
-      <c r="AD23" s="41"/>
-      <c r="AE23" s="42"/>
-      <c r="AF23" s="42"/>
-      <c r="AG23" s="46"/>
+      <c r="Q23" s="22"/>
+      <c r="R23" s="22"/>
+      <c r="S23" s="22"/>
+      <c r="T23" s="22"/>
+      <c r="U23" s="22"/>
+      <c r="V23" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="W23" s="22"/>
+      <c r="X23" s="22"/>
+      <c r="Y23" s="22"/>
+      <c r="Z23" s="22"/>
+      <c r="AC23" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD23" s="37"/>
+      <c r="AE23" s="38"/>
+      <c r="AF23" s="38"/>
+      <c r="AG23" s="43"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="13.2" spans="1:33">
-      <c r="A24" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" s="25"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26" t="s">
+      <c r="A24" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25" t="s">
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
-      <c r="N24" s="25"/>
-      <c r="O24" s="25"/>
-      <c r="P24" s="25" t="s">
+      <c r="F24" s="22"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="Q24" s="25"/>
-      <c r="R24" s="25"/>
-      <c r="S24" s="25"/>
-      <c r="T24" s="25"/>
-      <c r="U24" s="25"/>
-      <c r="V24" s="25"/>
-      <c r="W24" s="25"/>
-      <c r="X24" s="25"/>
-      <c r="Y24" s="25"/>
-      <c r="Z24" s="25"/>
-      <c r="AA24" s="25" t="s">
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="AB24" s="25"/>
-      <c r="AC24" s="40"/>
-      <c r="AD24" s="41"/>
-      <c r="AE24" s="42"/>
-      <c r="AF24" s="42"/>
-      <c r="AG24" s="46"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q24" s="22"/>
+      <c r="R24" s="22"/>
+      <c r="S24" s="22"/>
+      <c r="T24" s="22"/>
+      <c r="U24" s="22"/>
+      <c r="V24" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="W24" s="22"/>
+      <c r="X24" s="22"/>
+      <c r="Y24" s="22"/>
+      <c r="Z24" s="22"/>
+      <c r="AB24" s="22"/>
+      <c r="AC24" s="39"/>
+      <c r="AD24" s="37"/>
+      <c r="AE24" s="38"/>
+      <c r="AF24" s="38"/>
+      <c r="AG24" s="43"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:29">
-      <c r="A25" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="28"/>
+      <c r="A25" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="25"/>
       <c r="E25" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="27"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="27"/>
-      <c r="W25" s="27"/>
-      <c r="X25" s="27"/>
-      <c r="Y25" s="27"/>
-      <c r="Z25" s="27"/>
-      <c r="AA25" s="43"/>
-      <c r="AB25" s="44"/>
-      <c r="AC25" s="28"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="L25" s="24"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
+      <c r="S25" s="24"/>
+      <c r="T25" s="24"/>
+      <c r="U25" s="24"/>
+      <c r="V25" s="24"/>
+      <c r="W25" s="24"/>
+      <c r="X25" s="24"/>
+      <c r="Y25" s="24"/>
+      <c r="Z25" s="24"/>
+      <c r="AA25" s="40"/>
+      <c r="AB25" s="41"/>
+      <c r="AC25" s="25"/>
     </row>
     <row r="26" spans="1:29">
-      <c r="A26" s="29"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="29"/>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="45"/>
-      <c r="AB26" s="45"/>
-      <c r="AC26" s="29"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="26"/>
+      <c r="S26" s="26"/>
+      <c r="T26" s="26"/>
+      <c r="U26" s="26"/>
+      <c r="V26" s="26"/>
+      <c r="W26" s="26"/>
+      <c r="X26" s="26"/>
+      <c r="Y26" s="26"/>
+      <c r="Z26" s="26"/>
+      <c r="AA26" s="42"/>
+      <c r="AB26" s="42"/>
+      <c r="AC26" s="26"/>
     </row>
     <row r="27" spans="1:29">
-      <c r="A27" s="29"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="29"/>
-      <c r="N27" s="29"/>
-      <c r="O27" s="29"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="29"/>
-      <c r="S27" s="29"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="29"/>
-      <c r="W27" s="29"/>
-      <c r="X27" s="29"/>
-      <c r="Y27" s="29"/>
-      <c r="Z27" s="29"/>
-      <c r="AA27" s="29"/>
-      <c r="AB27" s="29"/>
-      <c r="AC27" s="29"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="26"/>
+      <c r="S27" s="26"/>
+      <c r="T27" s="26"/>
+      <c r="U27" s="26"/>
+      <c r="V27" s="26"/>
+      <c r="W27" s="26"/>
+      <c r="X27" s="26"/>
+      <c r="Y27" s="26"/>
+      <c r="Z27" s="26"/>
+      <c r="AA27" s="26"/>
+      <c r="AB27" s="26"/>
+      <c r="AC27" s="26"/>
     </row>
     <row r="28" spans="1:29">
-      <c r="A28" s="29"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
-      <c r="M28" s="29"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="29"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="29"/>
-      <c r="W28" s="29"/>
-      <c r="X28" s="29"/>
-      <c r="Y28" s="29"/>
-      <c r="Z28" s="29"/>
-      <c r="AA28" s="29"/>
-      <c r="AB28" s="29"/>
-      <c r="AC28" s="29"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="26"/>
+      <c r="S28" s="26"/>
+      <c r="T28" s="26"/>
+      <c r="U28" s="26"/>
+      <c r="V28" s="26"/>
+      <c r="W28" s="26"/>
+      <c r="X28" s="26"/>
+      <c r="Y28" s="26"/>
+      <c r="Z28" s="26"/>
+      <c r="AA28" s="26"/>
+      <c r="AB28" s="26"/>
+      <c r="AC28" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="27">

--- a/mca_sem/static/TR/MCA_1_TR_FORMATE.xlsx
+++ b/mca_sem/static/TR/MCA_1_TR_FORMATE.xlsx
@@ -167,7 +167,7 @@
     <t>2418M240007</t>
   </si>
   <si>
-    <t>No. of Candidate:  05</t>
+    <t>No. of Students:  05</t>
   </si>
   <si>
     <t>First Class with Distinction:</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">Address </t>
   </si>
   <si>
-    <t>Qualified: 04</t>
+    <t>Qualified:</t>
   </si>
   <si>
     <t>Pass: 04</t>
@@ -1778,7 +1778,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1" spans="1:29">
+    <row r="8" ht="61" customHeight="1" spans="1:29">
       <c r="A8" s="12" t="s">
         <v>17</v>
       </c>
